--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-26</t>
+          <t>Generado el 2026-08-28</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-28</t>
+          <t>Generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-31</t>
+          <t>Generado el 2026-09-01</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$G$496</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$496</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -631,15 +631,27 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>¿Sigue en el corpus?</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>columna interna: en_corpus_actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Generado el 2026-09-01</t>
         </is>
@@ -656,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G496"/>
+  <dimension ref="A1:H496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -666,6 +678,7 @@
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -704,6 +717,11 @@
           <t>Cuándo</t>
         </is>
       </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>¿Sigue en el corpus?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -741,6 +759,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -778,6 +801,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -815,6 +843,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -852,6 +885,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -889,6 +927,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -926,6 +969,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -963,6 +1011,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1000,6 +1053,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1037,6 +1095,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1074,6 +1137,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1111,6 +1179,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1148,6 +1221,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1185,6 +1263,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1222,6 +1305,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1259,6 +1347,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1296,6 +1389,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1333,6 +1431,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1370,6 +1473,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1407,6 +1515,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1444,6 +1557,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1481,6 +1599,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1518,6 +1641,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1555,6 +1683,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1592,6 +1725,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1629,6 +1767,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1666,6 +1809,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1703,6 +1851,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1740,6 +1893,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1777,6 +1935,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1814,6 +1977,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1851,6 +2019,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1888,6 +2061,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1925,6 +2103,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1962,6 +2145,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1999,6 +2187,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2036,6 +2229,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2073,6 +2271,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2110,6 +2313,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2147,6 +2355,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2184,6 +2397,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2221,6 +2439,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2258,6 +2481,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2295,6 +2523,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2332,6 +2565,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2369,6 +2607,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2406,6 +2649,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2443,6 +2691,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2480,6 +2733,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2517,6 +2775,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2554,6 +2817,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2591,6 +2859,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2628,6 +2901,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2665,6 +2943,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2702,6 +2985,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2739,6 +3027,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2776,6 +3069,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2813,6 +3111,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2850,6 +3153,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2887,6 +3195,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2924,6 +3237,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2961,6 +3279,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2998,6 +3321,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3035,6 +3363,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3072,6 +3405,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3109,6 +3447,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3146,6 +3489,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3183,6 +3531,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3220,6 +3573,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3257,6 +3615,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3294,6 +3657,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3331,6 +3699,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3368,6 +3741,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3405,6 +3783,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3442,6 +3825,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3479,6 +3867,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3516,6 +3909,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3553,6 +3951,11 @@
           <t>2026-08-05 22:23</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3590,6 +3993,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3627,6 +4035,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3664,6 +4077,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3701,6 +4119,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3738,6 +4161,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3775,6 +4203,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3812,6 +4245,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3849,6 +4287,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3886,6 +4329,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3923,6 +4371,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3960,6 +4413,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3997,6 +4455,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4034,6 +4497,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4071,6 +4539,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4108,6 +4581,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4145,6 +4623,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4182,6 +4665,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4219,6 +4707,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4256,6 +4749,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4293,6 +4791,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4330,6 +4833,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4367,6 +4875,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4404,6 +4917,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4441,6 +4959,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4478,6 +5001,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4515,6 +5043,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4552,6 +5085,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4589,6 +5127,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4626,6 +5169,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4663,6 +5211,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4700,6 +5253,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4737,6 +5295,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4774,6 +5337,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4811,6 +5379,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4848,6 +5421,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4885,6 +5463,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4922,6 +5505,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4959,6 +5547,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4996,6 +5589,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5033,6 +5631,11 @@
           <t>2026-08-05 22:25</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5070,6 +5673,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5107,6 +5715,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5144,6 +5757,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5181,6 +5799,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5218,6 +5841,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5255,6 +5883,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5292,6 +5925,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5329,6 +5967,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5366,6 +6009,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5403,6 +6051,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5440,6 +6093,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5477,6 +6135,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5514,6 +6177,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5551,6 +6219,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5588,6 +6261,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5625,6 +6303,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5662,6 +6345,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5699,6 +6387,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5736,6 +6429,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5773,6 +6471,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5810,6 +6513,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5847,6 +6555,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5884,6 +6597,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5921,6 +6639,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5958,6 +6681,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5995,6 +6723,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6032,6 +6765,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6069,6 +6807,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6106,6 +6849,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6143,6 +6891,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6180,6 +6933,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6217,6 +6975,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6254,6 +7017,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6291,6 +7059,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6328,6 +7101,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6365,6 +7143,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6402,6 +7185,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6439,6 +7227,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6476,6 +7269,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6513,6 +7311,11 @@
           <t>2026-08-05 22:45</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6550,6 +7353,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6587,6 +7395,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6624,6 +7437,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6661,6 +7479,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6698,6 +7521,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6735,6 +7563,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6772,6 +7605,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6809,6 +7647,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6846,6 +7689,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6883,6 +7731,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6920,6 +7773,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6957,6 +7815,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6994,6 +7857,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7031,6 +7899,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7068,6 +7941,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7105,6 +7983,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7142,6 +8025,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7179,6 +8067,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7216,6 +8109,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7253,6 +8151,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7290,6 +8193,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7327,6 +8235,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7364,6 +8277,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7401,6 +8319,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7438,6 +8361,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7475,6 +8403,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7512,6 +8445,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7549,6 +8487,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7586,6 +8529,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7623,6 +8571,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7660,6 +8613,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7697,6 +8655,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7734,6 +8697,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7771,6 +8739,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7808,6 +8781,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7845,6 +8823,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7882,6 +8865,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7919,6 +8907,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7956,6 +8949,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7993,6 +8991,11 @@
           <t>2026-08-05 22:46</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8030,6 +9033,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8067,6 +9075,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8104,6 +9117,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8141,6 +9159,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8178,6 +9201,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8215,6 +9243,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8252,6 +9285,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8289,6 +9327,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8326,6 +9369,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8363,6 +9411,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8400,6 +9453,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8437,6 +9495,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8474,6 +9537,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8511,6 +9579,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8548,6 +9621,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8585,6 +9663,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8622,6 +9705,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8659,6 +9747,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8696,6 +9789,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8733,6 +9831,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8770,6 +9873,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8807,6 +9915,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8844,6 +9957,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8881,6 +9999,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8918,6 +10041,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8955,6 +10083,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8992,6 +10125,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9029,6 +10167,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9066,6 +10209,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9103,6 +10251,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9140,6 +10293,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9177,6 +10335,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9214,6 +10377,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9251,6 +10419,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9288,6 +10461,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9325,6 +10503,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9362,6 +10545,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9399,6 +10587,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9436,6 +10629,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9473,6 +10671,11 @@
           <t>2026-08-05 22:47</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9510,6 +10713,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9547,6 +10755,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9584,6 +10797,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9621,6 +10839,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9658,6 +10881,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9695,6 +10923,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9732,6 +10965,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9769,6 +11007,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9806,6 +11049,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9843,6 +11091,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9880,6 +11133,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9917,6 +11175,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9954,6 +11217,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9991,6 +11259,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10028,6 +11301,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10065,6 +11343,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10102,6 +11385,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10139,6 +11427,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10176,6 +11469,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10213,6 +11511,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10250,6 +11553,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -10287,6 +11595,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10324,6 +11637,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10361,6 +11679,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -10398,6 +11721,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -10435,6 +11763,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -10472,6 +11805,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -10509,6 +11847,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10546,6 +11889,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10583,6 +11931,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10620,6 +11973,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10657,6 +12015,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10694,6 +12057,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10731,6 +12099,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10768,6 +12141,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10805,6 +12183,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10842,6 +12225,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10879,6 +12267,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10916,6 +12309,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10953,6 +12351,11 @@
           <t>2026-08-05 22:48</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10990,6 +12393,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11027,6 +12435,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11064,6 +12477,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11101,6 +12519,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -11138,6 +12561,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11175,6 +12603,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -11212,6 +12645,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -11249,6 +12687,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11286,6 +12729,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -11323,6 +12771,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -11360,6 +12813,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -11397,6 +12855,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -11434,6 +12897,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -11471,6 +12939,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -11508,6 +12981,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -11545,6 +13023,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11582,6 +13065,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11619,6 +13107,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11656,6 +13149,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11693,6 +13191,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11730,6 +13233,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11767,6 +13275,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11804,6 +13317,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11841,6 +13359,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11878,6 +13401,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11915,6 +13443,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11952,6 +13485,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11989,6 +13527,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -12026,6 +13569,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -12063,6 +13611,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -12100,6 +13653,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -12137,6 +13695,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -12174,6 +13737,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12211,6 +13779,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -12248,6 +13821,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -12285,6 +13863,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -12322,6 +13905,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -12359,6 +13947,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -12396,6 +13989,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -12433,6 +14031,11 @@
           <t>2026-08-05 22:49</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -12470,6 +14073,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -12507,6 +14115,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -12544,6 +14157,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12581,6 +14199,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12618,6 +14241,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12655,6 +14283,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12692,6 +14325,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12729,6 +14367,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12766,6 +14409,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12803,6 +14451,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12840,6 +14493,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12877,6 +14535,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12914,6 +14577,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12951,6 +14619,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12988,6 +14661,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -13025,6 +14703,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -13062,6 +14745,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -13099,6 +14787,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -13136,6 +14829,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -13173,6 +14871,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -13210,6 +14913,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -13247,6 +14955,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -13284,6 +14997,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -13321,6 +15039,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -13358,6 +15081,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -13395,6 +15123,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -13432,6 +15165,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -13469,6 +15207,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -13506,6 +15249,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -13543,6 +15291,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -13580,6 +15333,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -13617,6 +15375,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -13654,6 +15417,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13691,6 +15459,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -13728,6 +15501,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -13765,6 +15543,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -13802,6 +15585,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -13839,6 +15627,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -13876,6 +15669,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -13913,6 +15711,11 @@
           <t>2026-08-05 22:50</t>
         </is>
       </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13950,6 +15753,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13987,6 +15795,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14024,6 +15837,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -14061,6 +15879,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -14098,6 +15921,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -14135,6 +15963,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -14172,6 +16005,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -14209,6 +16047,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -14246,6 +16089,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -14283,6 +16131,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -14320,6 +16173,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -14357,6 +16215,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -14394,6 +16257,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -14431,6 +16299,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -14468,6 +16341,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -14505,6 +16383,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -14542,6 +16425,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -14579,6 +16467,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -14616,6 +16509,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -14653,6 +16551,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -14690,6 +16593,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -14727,6 +16635,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -14764,6 +16677,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -14801,6 +16719,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14838,6 +16761,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -14875,6 +16803,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -14912,6 +16845,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -14949,6 +16887,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -14986,6 +16929,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -15023,6 +16971,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -15060,6 +17013,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -15097,6 +17055,11 @@
           <t>2026-08-05 22:51</t>
         </is>
       </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -15134,6 +17097,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -15171,6 +17139,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -15208,6 +17181,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -15245,6 +17223,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -15282,6 +17265,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -15319,6 +17307,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -15356,6 +17349,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -15393,6 +17391,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -15430,6 +17433,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -15467,6 +17475,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -15504,6 +17517,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -15541,6 +17559,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -15578,6 +17601,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -15615,6 +17643,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -15652,6 +17685,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -15689,6 +17727,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -15726,6 +17769,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -15763,6 +17811,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -15800,6 +17853,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -15837,6 +17895,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -15874,6 +17937,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -15911,6 +17979,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -15948,6 +18021,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -15985,6 +18063,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -16022,6 +18105,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -16059,6 +18147,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -16096,6 +18189,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -16133,6 +18231,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -16170,6 +18273,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -16207,6 +18315,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -16244,6 +18357,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -16281,6 +18399,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -16318,6 +18441,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -16355,6 +18483,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -16392,6 +18525,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -16429,6 +18567,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -16466,6 +18609,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -16503,6 +18651,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -16540,6 +18693,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -16577,6 +18735,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -16614,6 +18777,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -16651,6 +18819,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -16688,6 +18861,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -16725,6 +18903,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -16762,6 +18945,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -16799,6 +18987,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -16836,6 +19029,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -16873,6 +19071,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -16910,6 +19113,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -16947,6 +19155,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -16984,6 +19197,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -17021,6 +19239,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -17058,6 +19281,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -17095,6 +19323,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -17132,6 +19365,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -17169,6 +19407,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -17206,6 +19449,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -17243,6 +19491,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -17280,6 +19533,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -17317,6 +19575,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -17354,6 +19617,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -17391,6 +19659,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -17428,6 +19701,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -17465,6 +19743,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -17502,6 +19785,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -17539,6 +19827,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -17576,6 +19869,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -17613,6 +19911,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -17650,6 +19953,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -17687,6 +19995,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -17724,6 +20037,11 @@
           <t>2026-08-05 22:52</t>
         </is>
       </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -17761,6 +20079,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -17798,6 +20121,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -17835,6 +20163,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -17872,6 +20205,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -17909,6 +20247,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -17946,6 +20289,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -17983,6 +20331,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -18020,6 +20373,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -18057,6 +20415,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -18094,6 +20457,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -18131,6 +20499,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -18168,6 +20541,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -18205,6 +20583,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -18242,6 +20625,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -18279,6 +20667,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -18316,6 +20709,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -18353,6 +20751,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -18390,6 +20793,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -18427,6 +20835,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -18464,6 +20877,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -18501,6 +20919,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -18538,6 +20961,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -18575,6 +21003,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -18612,6 +21045,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -18649,6 +21087,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -18686,6 +21129,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -18723,6 +21171,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -18760,6 +21213,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -18797,6 +21255,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -18834,6 +21297,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -18871,6 +21339,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -18908,6 +21381,11 @@
           <t>2026-08-11 08:14</t>
         </is>
       </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -18945,6 +21423,11 @@
           <t>2026-08-11 08:45</t>
         </is>
       </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -18982,6 +21465,11 @@
           <t>2026-08-11 08:45</t>
         </is>
       </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -19019,9 +21507,14 @@
           <t>2026-08-11 11:27</t>
         </is>
       </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G496"/>
+  <autoFilter ref="A1:H496"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -653,7 +653,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -521,139 +528,146 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>495 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: record_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Orden</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: orden</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Corriente (base o registro)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: corriente</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: verdict</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: reason</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Quién decidió</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: decided_by</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Cuándo</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: decided_at</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>¿Sigue en el corpus?</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: en_corpus_actual</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -682,42 +696,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Orden</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Corriente (base o registro)</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Quién decidió</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cuándo</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>¿Sigue en el corpus?</t>
         </is>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -667,7 +667,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -667,7 +667,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -506,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toda decisión de cribado por RESUMEN, una por fila, con su motivo y su marca de tiempo.</t>
+          <t>Cada decisión del cribado vigente por RESUMEN, una por fila, con su motivo y su marca de tiempo. Las emitió todas el modelo de lenguaje (Claude Opus 5) como revisor único, sin duplicación; «Quién decidió» lo dice fila a fila. Las 77 filas que «Quién decidió» marca como «heredada del brazo por PMID» llevan la fecha en que se copiaron al pozo (5 de agosto de 2026, a las 22:23), no la de la decisión: cada una repite, con el mismo veredicto y el mismo motivo, una decisión de resumen que el modelo tomó en la primera pasada. Llevan la etiqueta «LLM-assisted; pending human verification». Etiqueta original, transcrita tal cual. El modelo fue el revisor único, no un asistente, y la verificación humana que la etiqueta anuncia no se hizo para las exclusiones: de estas 77 filas, 11 son exclusiones; solo 2 las releyó un humano, porque cayeron en la muestra del recribado (D.V., a ciegas, en Rayyan), y las otras 9 no las releyó ningún humano. S19 explica de dónde salen. La primera pasada del 4 de agosto de 2026 sobre el brazo A de PubMed, que el cribado del pozo sustituyó, consta en el repositorio y no en S3 (S19), y con ella la fila que corrigió una exclusión errónea (S6).</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
+++ b/verificables revisión sistemática/S3_decisiones_etapa3_resumen.xlsx
@@ -667,7 +667,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
